--- a/s11列表.xlsx
+++ b/s11列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0194A9-B945-4FAE-BAF9-D214AD0CFEF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF5251F-72AC-4D0F-A423-9AC11423039C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{61E04213-F3AC-4663-A451-F13222CEB80E}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{61E04213-F3AC-4663-A451-F13222CEB80E}"/>
   </bookViews>
   <sheets>
     <sheet name="星" sheetId="1" r:id="rId1"/>
